--- a/cp-add_code-statut-recrutement/ig/ValueSet-eclaire-category-vs.xlsx
+++ b/cp-add_code-statut-recrutement/ig/ValueSet-eclaire-category-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:14:20+00:00</t>
+    <t>2025-11-27T09:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
